--- a/excell/steering_committee.xlsx
+++ b/excell/steering_committee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\MWSCAS Steering Committee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CCF552-FB22-4E1E-ACA9-021D5C68D000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5237FE04-D621-4DBA-9BCA-3C3143DC0C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="355">
   <si>
     <t>LastName</t>
   </si>
@@ -178,9 +178,6 @@
     <t>bibyk.jpg</t>
   </si>
   <si>
-    <t>Blain Christen</t>
-  </si>
-  <si>
     <t>Jennifer</t>
   </si>
   <si>
@@ -304,9 +301,6 @@
     <t>Antonio</t>
   </si>
   <si>
-    <t>DARPA</t>
-  </si>
-  <si>
     <t>617-710-4638</t>
   </si>
   <si>
@@ -982,9 +976,6 @@
     <t>Michael A.</t>
   </si>
   <si>
-    <t>Future Sumposia, Web Master</t>
-  </si>
-  <si>
     <t>202-903-0870</t>
   </si>
   <si>
@@ -1037,6 +1028,63 @@
   </si>
   <si>
     <t>The State University of New York at Stony Brook</t>
+  </si>
+  <si>
+    <t>Yazdi</t>
+  </si>
+  <si>
+    <t>Navid</t>
+  </si>
+  <si>
+    <t>734- 972-2959</t>
+  </si>
+  <si>
+    <t>yazdi@msu.edu</t>
+  </si>
+  <si>
+    <t>yazdi.jpg</t>
+  </si>
+  <si>
+    <t>Mason</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>517-355-6502</t>
+  </si>
+  <si>
+    <t>mason@msu.edu</t>
+  </si>
+  <si>
+    <t>mason.jpg</t>
+  </si>
+  <si>
+    <t>Siemens EDA</t>
+  </si>
+  <si>
+    <t>Blain</t>
+  </si>
+  <si>
+    <t>Banerjee</t>
+  </si>
+  <si>
+    <t>Aritra</t>
+  </si>
+  <si>
+    <t>University of Illinois Chicago</t>
+  </si>
+  <si>
+    <t>312-413-2283</t>
+  </si>
+  <si>
+    <t>abaner33@uic.edu</t>
+  </si>
+  <si>
+    <t>banerjee.jpg</t>
+  </si>
+  <si>
+    <t>Bylaws, Future Sumposia, Web Master</t>
   </si>
 </sst>
 </file>
@@ -1388,12 +1436,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
     <col min="2" max="2" width="16.1796875" customWidth="1"/>
-    <col min="3" max="3" width="26.36328125" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="64.08984375" customWidth="1"/>
     <col min="5" max="6" width="39.81640625" customWidth="1"/>
     <col min="7" max="7" width="29.54296875" customWidth="1"/>
@@ -1464,10 +1512,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -1559,1300 +1607,1378 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>348</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>349</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
+        <v>351</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>347</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>55</v>
+      </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>95</v>
+        <v>87</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>333</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>346</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>111</v>
+        <v>29</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="G21" t="s">
+        <v>115</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" t="s">
-        <v>128</v>
-      </c>
-      <c r="G22" t="s">
-        <v>129</v>
+        <v>60</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
+        <v>126</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
       </c>
       <c r="G24" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="I24" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>137</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="G25" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I26" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G27" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I27" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E28" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I28" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I29" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
       </c>
       <c r="G30" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I30" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>181</v>
+        <v>172</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="G31" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I31" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G32" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I32" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G33" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I33" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G34" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G35" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I35" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E36" t="s">
+        <v>203</v>
+      </c>
+      <c r="G36" t="s">
+        <v>204</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
         <v>205</v>
-      </c>
-      <c r="G36" t="s">
-        <v>211</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G37" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
-      </c>
-      <c r="G38" t="s">
-        <v>223</v>
+        <v>343</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I38" t="s">
-        <v>224</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E39" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="G39" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I39" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B40" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="E40" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="G40" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I40" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="D41" t="s">
-        <v>240</v>
+        <v>225</v>
+      </c>
+      <c r="E41" t="s">
+        <v>226</v>
       </c>
       <c r="G41" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I41" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="D42" t="s">
-        <v>245</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>246</v>
+        <v>232</v>
+      </c>
+      <c r="E42" t="s">
+        <v>233</v>
       </c>
       <c r="G42" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I42" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B43" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s">
-        <v>251</v>
+        <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E43" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="G43" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I43" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>257</v>
-      </c>
-      <c r="E44" t="s">
-        <v>258</v>
+        <v>243</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="G44" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I44" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>249</v>
       </c>
       <c r="D45" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="G45" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I45" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="E46" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="G46" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="G47" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I47" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="E48" t="s">
-        <v>281</v>
-      </c>
-      <c r="F48" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="G48" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I48" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B49" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E49" t="s">
-        <v>288</v>
-      </c>
-      <c r="F49" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="G49" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="E50" t="s">
-        <v>295</v>
+        <v>279</v>
+      </c>
+      <c r="F50" t="s">
+        <v>280</v>
       </c>
       <c r="G50" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="B51" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="E51" t="s">
-        <v>301</v>
+        <v>286</v>
+      </c>
+      <c r="F51" t="s">
+        <v>287</v>
       </c>
       <c r="G51" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I51" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B52" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="E52" t="s">
-        <v>307</v>
-      </c>
-      <c r="F52" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="G52" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I52" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="B53" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="E53" t="s">
-        <v>314</v>
-      </c>
-      <c r="F53" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="G53" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B54" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C54" t="s">
-        <v>320</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>66</v>
+        <v>304</v>
       </c>
       <c r="E54" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="F54" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="G54" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I54" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B55" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>311</v>
       </c>
       <c r="E55" t="s">
-        <v>327</v>
+        <v>312</v>
+      </c>
+      <c r="F55" t="s">
+        <v>313</v>
       </c>
       <c r="G55" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>316</v>
+      </c>
+      <c r="B56" t="s">
+        <v>317</v>
+      </c>
+      <c r="C56" t="s">
+        <v>354</v>
+      </c>
+      <c r="D56" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" t="s">
+        <v>318</v>
+      </c>
+      <c r="F56" t="s">
+        <v>319</v>
+      </c>
+      <c r="G56" t="s">
+        <v>320</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>322</v>
+      </c>
+      <c r="B57" t="s">
+        <v>323</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" t="s">
+        <v>324</v>
+      </c>
+      <c r="G57" t="s">
+        <v>325</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>336</v>
+      </c>
+      <c r="B58" t="s">
+        <v>337</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" t="s">
+        <v>338</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B59" t="s">
+        <v>328</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>329</v>
+      </c>
+      <c r="E59" t="s">
         <v>330</v>
       </c>
-      <c r="B56" t="s">
+      <c r="G59" t="s">
         <v>331</v>
       </c>
-      <c r="C56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="H59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
         <v>332</v>
-      </c>
-      <c r="E56" t="s">
-        <v>333</v>
-      </c>
-      <c r="G56" t="s">
-        <v>334</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" t="s">
-        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -2861,58 +2987,64 @@
     <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="H4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="H5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H11" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="H24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="H25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="H26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="H27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="H28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="H29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="H30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="H31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="H32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="H33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="H34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="H35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="H36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="H38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="H39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="H40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="H42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="H44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="H45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="H46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="H47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="H48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="H49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="H50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="H51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="H52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="H54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="H55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="H18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H19" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="H20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="H21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="H22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="H23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="H24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="H25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="H26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="H27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="H28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="H29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="H30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="H31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="H32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="H33" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="H34" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="H35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="H36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="H37" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="H39" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="H40" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="H41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="H42" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="H43" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="H44" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="H45" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="H46" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="H47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="H48" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="H49" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="H50" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="H51" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="H52" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="H53" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="H54" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="H55" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="H56" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="H57" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="H59" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
     <hyperlink ref="H6" r:id="rId56" xr:uid="{1528AAE4-D8AC-43A6-8202-1C14C2F4543E}"/>
+    <hyperlink ref="G58" r:id="rId57" xr:uid="{7401F541-37AB-402F-B517-5E2F4D804756}"/>
+    <hyperlink ref="H58" r:id="rId58" xr:uid="{B7ECF16E-341E-4D34-A84C-AEA63F8E0D67}"/>
+    <hyperlink ref="G38" r:id="rId59" xr:uid="{11EC35A0-60DA-46F9-B3D5-DC1443C39A1A}"/>
+    <hyperlink ref="H38" r:id="rId60" xr:uid="{2F48B289-2ABB-4EB8-8E8A-B0CF496AD02D}"/>
+    <hyperlink ref="G7" r:id="rId61" xr:uid="{D90A5E6D-EAF8-4FA1-A7FD-59D0A0F6C5D0}"/>
+    <hyperlink ref="H7" r:id="rId62" xr:uid="{4C685598-C4B2-4E9F-ADC9-41612D41B845}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excell/steering_committee.xlsx
+++ b/excell/steering_committee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\MWSCAS Steering Committee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5237FE04-D621-4DBA-9BCA-3C3143DC0C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB82FC7-F4A4-487C-80C7-620F0612D0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="361">
   <si>
     <t>LastName</t>
   </si>
@@ -1085,6 +1085,24 @@
   </si>
   <si>
     <t>Bylaws, Future Sumposia, Web Master</t>
+  </si>
+  <si>
+    <t>Shah</t>
+  </si>
+  <si>
+    <t>Sahil</t>
+  </si>
+  <si>
+    <t>University of Maryland</t>
+  </si>
+  <si>
+    <t>301-405-0772</t>
+  </si>
+  <si>
+    <t>sshah389@umd.edu</t>
+  </si>
+  <si>
+    <t>shah.jpg</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
@@ -2847,137 +2865,163 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E55" t="s">
-        <v>312</v>
-      </c>
-      <c r="F55" t="s">
-        <v>313</v>
-      </c>
-      <c r="G55" t="s">
-        <v>314</v>
+        <v>358</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B56" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C56" t="s">
-        <v>354</v>
+        <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>311</v>
       </c>
       <c r="E56" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F56" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G56" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I56" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B57" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>354</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E57" t="s">
-        <v>324</v>
+        <v>318</v>
+      </c>
+      <c r="F57" t="s">
+        <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I57" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B58" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>292</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>338</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>339</v>
+        <v>324</v>
+      </c>
+      <c r="G58" t="s">
+        <v>325</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I58" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>336</v>
+      </c>
+      <c r="B59" t="s">
+        <v>337</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>292</v>
+      </c>
+      <c r="E59" t="s">
+        <v>338</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>327</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>328</v>
       </c>
-      <c r="C59" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
         <v>329</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E60" t="s">
         <v>330</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G60" t="s">
         <v>331</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="H60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
         <v>332</v>
       </c>
     </row>
@@ -3034,17 +3078,19 @@
     <hyperlink ref="H52" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
     <hyperlink ref="H53" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
     <hyperlink ref="H54" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H55" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="H56" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="H57" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H59" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="H56" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="H57" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="H58" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="H60" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
     <hyperlink ref="H6" r:id="rId56" xr:uid="{1528AAE4-D8AC-43A6-8202-1C14C2F4543E}"/>
-    <hyperlink ref="G58" r:id="rId57" xr:uid="{7401F541-37AB-402F-B517-5E2F4D804756}"/>
-    <hyperlink ref="H58" r:id="rId58" xr:uid="{B7ECF16E-341E-4D34-A84C-AEA63F8E0D67}"/>
+    <hyperlink ref="G59" r:id="rId57" xr:uid="{7401F541-37AB-402F-B517-5E2F4D804756}"/>
+    <hyperlink ref="H59" r:id="rId58" xr:uid="{B7ECF16E-341E-4D34-A84C-AEA63F8E0D67}"/>
     <hyperlink ref="G38" r:id="rId59" xr:uid="{11EC35A0-60DA-46F9-B3D5-DC1443C39A1A}"/>
     <hyperlink ref="H38" r:id="rId60" xr:uid="{2F48B289-2ABB-4EB8-8E8A-B0CF496AD02D}"/>
     <hyperlink ref="G7" r:id="rId61" xr:uid="{D90A5E6D-EAF8-4FA1-A7FD-59D0A0F6C5D0}"/>
     <hyperlink ref="H7" r:id="rId62" xr:uid="{4C685598-C4B2-4E9F-ADC9-41612D41B845}"/>
+    <hyperlink ref="G55" r:id="rId63" xr:uid="{AC8EC2B0-D276-406A-BAC2-F7A25AF626A3}"/>
+    <hyperlink ref="H55" r:id="rId64" xr:uid="{7EA71D21-1BD4-47D0-A613-B485B498D443}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excell/steering_committee.xlsx
+++ b/excell/steering_committee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\MWSCAS Steering Committee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB82FC7-F4A4-487C-80C7-620F0612D0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E630820-5CBE-4190-A12C-69FF5AEECD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="387">
   <si>
     <t>LastName</t>
   </si>
@@ -286,9 +286,6 @@
     <t>University of Seville</t>
   </si>
   <si>
-    <t>+34954466666</t>
-  </si>
-  <si>
     <t>jrosa@imse-cnm.csic.es</t>
   </si>
   <si>
@@ -1103,6 +1100,87 @@
   </si>
   <si>
     <t>shah.jpg</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>MWSCAS Steering Committee Directory</t>
+  </si>
+  <si>
+    <t>The MWSCAS Steering Committee provides long-term guidance for the IEEE International Midwest Symposium on Circuits and Systems.</t>
+  </si>
+  <si>
+    <t>Cavallaro</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Rice University</t>
+  </si>
+  <si>
+    <t>713-348-4719</t>
+  </si>
+  <si>
+    <t>cavallar@rice.edu</t>
+  </si>
+  <si>
+    <t>Jinghong</t>
+  </si>
+  <si>
+    <t>University of Houston</t>
+  </si>
+  <si>
+    <t>713-743-6096</t>
+  </si>
+  <si>
+    <t>jinghong@uh.edu</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Garrett</t>
+  </si>
+  <si>
+    <t>865-974-3132</t>
+  </si>
+  <si>
+    <t>garose@utk.edu</t>
+  </si>
+  <si>
+    <t>rose.jpg</t>
+  </si>
+  <si>
+    <t>chen1.jpg</t>
+  </si>
+  <si>
+    <t>cavallaro.jpg</t>
+  </si>
+  <si>
+    <t>Walling</t>
+  </si>
+  <si>
+    <t>Jeffery</t>
+  </si>
+  <si>
+    <t>Virginia Tech University</t>
+  </si>
+  <si>
+    <t>540-231-4786</t>
+  </si>
+  <si>
+    <t>jswalling@vt.edu</t>
+  </si>
+  <si>
+    <t>walling.jpg</t>
+  </si>
+  <si>
+    <t>+34 954 46 66 66</t>
   </si>
 </sst>
 </file>
@@ -1454,1643 +1532,1772 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
     <col min="2" max="2" width="16.1796875" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="64.08984375" customWidth="1"/>
-    <col min="5" max="6" width="39.81640625" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" customWidth="1"/>
+    <col min="4" max="4" width="35.36328125" customWidth="1"/>
+    <col min="5" max="5" width="22.90625" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="29.54296875" customWidth="1"/>
-    <col min="8" max="8" width="52.90625" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>362</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>334</v>
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>334</v>
+      </c>
+      <c r="E5" t="s">
+        <v>333</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>348</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>352</v>
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>353</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>347</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>348</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>349</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>50</v>
+        <v>350</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>49</v>
+      </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
         <v>14</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>364</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>365</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" t="s">
-        <v>89</v>
+        <v>366</v>
+      </c>
+      <c r="E16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>90</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>369</v>
       </c>
       <c r="C17" t="s">
-        <v>333</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" t="s">
-        <v>94</v>
+        <v>371</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I18" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>109</v>
+        <v>87</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>332</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>345</v>
+      </c>
+      <c r="E21" t="s">
+        <v>92</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>119</v>
+        <v>97</v>
+      </c>
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" t="s">
+        <v>99</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" t="s">
-        <v>126</v>
+        <v>29</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I24" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="I25" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" t="s">
-        <v>145</v>
+        <v>60</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I26" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>123</v>
+      </c>
+      <c r="E27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" t="s">
+        <v>125</v>
       </c>
       <c r="G27" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I28" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>161</v>
+        <v>136</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="G29" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="I29" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
-      </c>
-      <c r="E30" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="G30" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I30" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>153</v>
+      </c>
+      <c r="E32" t="s">
+        <v>154</v>
       </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I32" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I33" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="C34" t="s">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="G34" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>196</v>
-      </c>
-      <c r="E35" t="s">
-        <v>197</v>
+        <v>171</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I35" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="D36" t="s">
-        <v>202</v>
-      </c>
-      <c r="E36" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="G36" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I36" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G37" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>341</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="D38" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>343</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>344</v>
+        <v>190</v>
+      </c>
+      <c r="G38" t="s">
+        <v>191</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I38" t="s">
-        <v>345</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="G39" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I39" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="G40" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I40" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C41" t="s">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="E41" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="G41" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I41" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="C42" t="s">
-        <v>231</v>
+        <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="E42" t="s">
-        <v>233</v>
-      </c>
-      <c r="G42" t="s">
-        <v>234</v>
+        <v>342</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I42" t="s">
-        <v>235</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>238</v>
+        <v>212</v>
+      </c>
+      <c r="E43" t="s">
+        <v>213</v>
       </c>
       <c r="G43" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I43" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>243</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>244</v>
+        <v>218</v>
+      </c>
+      <c r="E44" t="s">
+        <v>219</v>
       </c>
       <c r="G44" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I44" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="B45" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="C45" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="D45" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="G45" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I45" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="E46" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="G46" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="B47" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
-      </c>
-      <c r="E47" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="G47" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I47" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>266</v>
-      </c>
-      <c r="E48" t="s">
-        <v>267</v>
+        <v>242</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="G48" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I48" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B49" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="D49" t="s">
-        <v>272</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="G49" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B50" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="E50" t="s">
-        <v>279</v>
-      </c>
-      <c r="F50" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="G50" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="E51" t="s">
-        <v>286</v>
-      </c>
-      <c r="F51" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="G51" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I51" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="B52" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="E52" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="G52" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I52" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="B53" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="E53" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="G53" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="B54" t="s">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="E54" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="F54" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="G54" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I54" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>357</v>
+        <v>218</v>
       </c>
       <c r="E55" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="B56" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="E56" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="F56" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="G56" t="s">
-        <v>314</v>
+        <v>287</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I56" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="B57" t="s">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="C57" t="s">
-        <v>354</v>
+        <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>291</v>
       </c>
       <c r="E57" t="s">
-        <v>318</v>
-      </c>
-      <c r="F57" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="G57" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I57" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="B58" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="E58" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="G58" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I58" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="B59" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="C59" t="s">
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="E59" t="s">
-        <v>338</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>339</v>
+        <v>304</v>
+      </c>
+      <c r="F59" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" t="s">
+        <v>306</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I59" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>354</v>
+      </c>
+      <c r="B60" t="s">
+        <v>355</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
+        <v>356</v>
+      </c>
+      <c r="E60" t="s">
+        <v>357</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>308</v>
+      </c>
+      <c r="B61" t="s">
+        <v>309</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>310</v>
+      </c>
+      <c r="E61" t="s">
+        <v>311</v>
+      </c>
+      <c r="F61" t="s">
+        <v>312</v>
+      </c>
+      <c r="G61" t="s">
+        <v>313</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>315</v>
+      </c>
+      <c r="B62" t="s">
+        <v>316</v>
+      </c>
+      <c r="C62" t="s">
+        <v>353</v>
+      </c>
+      <c r="D62" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" t="s">
+        <v>317</v>
+      </c>
+      <c r="F62" t="s">
+        <v>318</v>
+      </c>
+      <c r="G62" t="s">
+        <v>319</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>321</v>
+      </c>
+      <c r="B63" t="s">
+        <v>322</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" t="s">
+        <v>323</v>
+      </c>
+      <c r="G63" t="s">
+        <v>324</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>380</v>
+      </c>
+      <c r="B64" t="s">
+        <v>381</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
+        <v>382</v>
+      </c>
+      <c r="E64" t="s">
+        <v>383</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>335</v>
+      </c>
+      <c r="B65" t="s">
+        <v>336</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>291</v>
+      </c>
+      <c r="E65" t="s">
+        <v>337</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>326</v>
+      </c>
+      <c r="B66" t="s">
         <v>327</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
         <v>328</v>
       </c>
-      <c r="C60" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="E66" t="s">
         <v>329</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G66" t="s">
         <v>330</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" t="s">
         <v>331</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" t="s">
-        <v>332</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H19" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="H25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="H26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="H27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="H28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="H29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="H30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="H31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="H32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="H33" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="H34" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="H35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="H36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="H37" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H39" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="H40" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="H41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="H42" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H43" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="H44" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H45" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="H46" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="H47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="H48" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="H49" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="H50" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="H51" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="H52" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="H53" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="H54" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H56" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="H57" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="H58" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H60" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="H6" r:id="rId56" xr:uid="{1528AAE4-D8AC-43A6-8202-1C14C2F4543E}"/>
-    <hyperlink ref="G59" r:id="rId57" xr:uid="{7401F541-37AB-402F-B517-5E2F4D804756}"/>
-    <hyperlink ref="H59" r:id="rId58" xr:uid="{B7ECF16E-341E-4D34-A84C-AEA63F8E0D67}"/>
-    <hyperlink ref="G38" r:id="rId59" xr:uid="{11EC35A0-60DA-46F9-B3D5-DC1443C39A1A}"/>
-    <hyperlink ref="H38" r:id="rId60" xr:uid="{2F48B289-2ABB-4EB8-8E8A-B0CF496AD02D}"/>
-    <hyperlink ref="G7" r:id="rId61" xr:uid="{D90A5E6D-EAF8-4FA1-A7FD-59D0A0F6C5D0}"/>
-    <hyperlink ref="H7" r:id="rId62" xr:uid="{4C685598-C4B2-4E9F-ADC9-41612D41B845}"/>
-    <hyperlink ref="G55" r:id="rId63" xr:uid="{AC8EC2B0-D276-406A-BAC2-F7A25AF626A3}"/>
-    <hyperlink ref="H55" r:id="rId64" xr:uid="{7EA71D21-1BD4-47D0-A613-B485B498D443}"/>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H18" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H19" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H20" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="H22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="H24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="H25" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="H26" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="H27" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="H28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="H29" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="H30" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="H31" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="H32" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="H33" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="H34" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="H35" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="H36" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="H37" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="H38" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="H39" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="H40" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="H41" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="H43" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="H44" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="H45" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="H46" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="H47" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="H48" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="H49" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="H50" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="H51" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="H52" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="H53" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="H54" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="H56" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="H57" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="H58" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="H59" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="H61" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="H62" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="H63" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="H66" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="H8" r:id="rId56" xr:uid="{1528AAE4-D8AC-43A6-8202-1C14C2F4543E}"/>
+    <hyperlink ref="G65" r:id="rId57" xr:uid="{7401F541-37AB-402F-B517-5E2F4D804756}"/>
+    <hyperlink ref="H65" r:id="rId58" xr:uid="{B7ECF16E-341E-4D34-A84C-AEA63F8E0D67}"/>
+    <hyperlink ref="G42" r:id="rId59" xr:uid="{11EC35A0-60DA-46F9-B3D5-DC1443C39A1A}"/>
+    <hyperlink ref="H42" r:id="rId60" xr:uid="{2F48B289-2ABB-4EB8-8E8A-B0CF496AD02D}"/>
+    <hyperlink ref="G9" r:id="rId61" xr:uid="{D90A5E6D-EAF8-4FA1-A7FD-59D0A0F6C5D0}"/>
+    <hyperlink ref="H9" r:id="rId62" xr:uid="{4C685598-C4B2-4E9F-ADC9-41612D41B845}"/>
+    <hyperlink ref="G60" r:id="rId63" xr:uid="{AC8EC2B0-D276-406A-BAC2-F7A25AF626A3}"/>
+    <hyperlink ref="H60" r:id="rId64" xr:uid="{7EA71D21-1BD4-47D0-A613-B485B498D443}"/>
+    <hyperlink ref="G15" r:id="rId65" xr:uid="{2AF63012-332E-4D49-A2B4-55E8C657F164}"/>
+    <hyperlink ref="G16" r:id="rId66" xr:uid="{7812C9C1-1DCB-42C8-A0FE-2A6F2260568E}"/>
+    <hyperlink ref="G17" r:id="rId67" xr:uid="{A91810D6-E920-448C-B0A7-73E5E54B7139}"/>
+    <hyperlink ref="H17" r:id="rId68" xr:uid="{88816AA8-236E-4423-91F7-F6965E4C61BF}"/>
+    <hyperlink ref="G55" r:id="rId69" xr:uid="{4A9471CD-0C02-4650-8813-ACB45A47F5FC}"/>
+    <hyperlink ref="H55" r:id="rId70" xr:uid="{36042A37-92CD-4D49-BB59-54B6C24534F2}"/>
+    <hyperlink ref="G64" r:id="rId71" xr:uid="{9E44216B-DE59-4FDD-B08A-E404036ABB8C}"/>
+    <hyperlink ref="H64" r:id="rId72" xr:uid="{9C5482F5-FE5A-45F4-8DCC-85B4C5178846}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excell/steering_committee.xlsx
+++ b/excell/steering_committee.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\MWSCAS Steering Committee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E630820-5CBE-4190-A12C-69FF5AEECD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419613F7-E63F-4180-9B85-97B9064C9BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="387">
   <si>
     <t>LastName</t>
   </si>
@@ -640,9 +640,6 @@
     <t>Mandal</t>
   </si>
   <si>
-    <t>Surnyejk</t>
-  </si>
-  <si>
     <t>Brookhaven National Laboratory</t>
   </si>
   <si>
@@ -1181,6 +1178,9 @@
   </si>
   <si>
     <t>+34 954 46 66 66</t>
+  </si>
+  <si>
+    <t>Soumyajit</t>
   </si>
 </sst>
 </file>
@@ -1548,18 +1548,18 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" t="s">
         <v>360</v>
-      </c>
-      <c r="D1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D2" t="s">
         <v>362</v>
-      </c>
-      <c r="D2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -1625,10 +1625,10 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1720,28 +1720,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" t="s">
         <v>347</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>348</v>
       </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>349</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
         <v>351</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1798,7 +1798,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B12" t="s">
         <v>52</v>
@@ -1903,28 +1903,28 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" t="s">
         <v>364</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
         <v>365</v>
       </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>366</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="H16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1932,25 +1932,25 @@
         <v>74</v>
       </c>
       <c r="B17" t="s">
+        <v>368</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
         <v>369</v>
       </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>370</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="H17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -2016,7 +2016,7 @@
         <v>87</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G20" t="s">
         <v>88</v>
@@ -2036,10 +2036,10 @@
         <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E21" t="s">
         <v>92</v>
@@ -2541,264 +2541,264 @@
         <v>205</v>
       </c>
       <c r="B41" t="s">
+        <v>386</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
         <v>206</v>
-      </c>
-      <c r="C41" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" t="s">
-        <v>207</v>
       </c>
       <c r="E41" t="s">
         <v>202</v>
       </c>
       <c r="G41" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="s">
         <v>208</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" t="s">
         <v>340</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>290</v>
+      </c>
+      <c r="E42" t="s">
         <v>341</v>
       </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" t="s">
-        <v>291</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="G42" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" t="s">
         <v>343</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I42" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>209</v>
+      </c>
+      <c r="B43" t="s">
         <v>210</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
         <v>211</v>
       </c>
-      <c r="C43" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>212</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>213</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
         <v>214</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>215</v>
+      </c>
+      <c r="B44" t="s">
         <v>216</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
         <v>217</v>
       </c>
-      <c r="C44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>218</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>219</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
         <v>220</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>221</v>
+      </c>
+      <c r="B45" t="s">
         <v>222</v>
-      </c>
-      <c r="B45" t="s">
-        <v>223</v>
       </c>
       <c r="C45" t="s">
         <v>177</v>
       </c>
       <c r="D45" t="s">
+        <v>223</v>
+      </c>
+      <c r="E45" t="s">
         <v>224</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>225</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
         <v>226</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" t="s">
         <v>228</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>229</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>230</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>231</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>232</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" t="s">
         <v>233</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" t="s">
         <v>235</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
         <v>236</v>
       </c>
-      <c r="C47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="G47" t="s">
         <v>237</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="s">
         <v>238</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>239</v>
+      </c>
+      <c r="B48" t="s">
         <v>240</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="E48" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="G48" t="s">
         <v>243</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" t="s">
         <v>244</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>245</v>
+      </c>
+      <c r="B49" t="s">
         <v>246</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>247</v>
-      </c>
-      <c r="C49" t="s">
-        <v>248</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
       </c>
       <c r="E49" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" t="s">
         <v>249</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="s">
         <v>250</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>251</v>
+      </c>
+      <c r="B50" t="s">
         <v>252</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
         <v>253</v>
       </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>254</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>255</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" t="s">
         <v>256</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" t="s">
         <v>258</v>
-      </c>
-      <c r="B51" t="s">
-        <v>259</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
@@ -2807,325 +2807,325 @@
         <v>201</v>
       </c>
       <c r="E51" t="s">
+        <v>259</v>
+      </c>
+      <c r="G51" t="s">
         <v>260</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
         <v>261</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>262</v>
+      </c>
+      <c r="B52" t="s">
         <v>263</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
         <v>264</v>
       </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>265</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>266</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" t="s">
         <v>267</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>268</v>
+      </c>
+      <c r="B53" t="s">
         <v>269</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
         <v>270</v>
       </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>271</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>272</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
         <v>273</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>274</v>
+      </c>
+      <c r="B54" t="s">
         <v>275</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
         <v>276</v>
       </c>
-      <c r="C54" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>277</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>278</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>279</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" t="s">
         <v>280</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>372</v>
+      </c>
+      <c r="B55" t="s">
         <v>373</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>217</v>
+      </c>
+      <c r="E55" t="s">
         <v>374</v>
       </c>
-      <c r="C55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" t="s">
-        <v>218</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="G55" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" t="s">
         <v>376</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>281</v>
+      </c>
+      <c r="B56" t="s">
         <v>282</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
         <v>283</v>
       </c>
-      <c r="C56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>284</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>285</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>286</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" t="s">
         <v>287</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>288</v>
+      </c>
+      <c r="B57" t="s">
         <v>289</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
         <v>290</v>
       </c>
-      <c r="C57" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>291</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>292</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="s">
         <v>293</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>294</v>
+      </c>
+      <c r="B58" t="s">
         <v>295</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
         <v>296</v>
       </c>
-      <c r="C58" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>297</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>298</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
         <v>299</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>300</v>
+      </c>
+      <c r="B59" t="s">
         <v>301</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
         <v>302</v>
       </c>
-      <c r="C59" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>303</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>304</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>305</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
         <v>306</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" t="s">
         <v>354</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
         <v>355</v>
       </c>
-      <c r="C60" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>356</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="H60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
         <v>358</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>307</v>
+      </c>
+      <c r="B61" t="s">
         <v>308</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
         <v>309</v>
       </c>
-      <c r="C61" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>310</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>311</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>312</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="s">
         <v>313</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I61" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>314</v>
+      </c>
+      <c r="B62" t="s">
         <v>315</v>
       </c>
-      <c r="B62" t="s">
-        <v>316</v>
-      </c>
       <c r="C62" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
       </c>
       <c r="E62" t="s">
+        <v>316</v>
+      </c>
+      <c r="F62" t="s">
         <v>317</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>318</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
         <v>319</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" t="s">
         <v>321</v>
-      </c>
-      <c r="B63" t="s">
-        <v>322</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
@@ -3134,94 +3134,94 @@
         <v>23</v>
       </c>
       <c r="E63" t="s">
+        <v>322</v>
+      </c>
+      <c r="G63" t="s">
         <v>323</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" t="s">
         <v>324</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B64" t="s">
         <v>380</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
         <v>381</v>
       </c>
-      <c r="C64" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>382</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
         <v>384</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>334</v>
+      </c>
+      <c r="B65" t="s">
         <v>335</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>290</v>
+      </c>
+      <c r="E65" t="s">
         <v>336</v>
       </c>
-      <c r="C65" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" t="s">
-        <v>291</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="G65" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="H65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
         <v>338</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>325</v>
+      </c>
+      <c r="B66" t="s">
         <v>326</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
         <v>327</v>
       </c>
-      <c r="C66" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>328</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>329</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" t="s">
         <v>330</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>
